--- a/tests/fixtures/sample_tree/월간실적보고/2024/2024_월간실적보고_실적취합_진짜최종.xlsx
+++ b/tests/fixtures/sample_tree/월간실적보고/2024/2024_월간실적보고_실적취합_진짜최종.xlsx
@@ -535,39 +535,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>수질검사</t>
+          <t>처리건수</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>141</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>민원</t>
+          <t>완료율</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
